--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.4</t>
+    <t>1.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T07:53:37+00:00</t>
+    <t>2026-09-21T09:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.5</t>
+    <t>1.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T09:39:56+00:00</t>
+    <t>2026-10-09T09:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:40:46+00:00</t>
+    <t>2026-10-09T10:49:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-lmdi-encounter.xlsx
+++ b/StructureDefinition-lmdi-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.7</t>
+    <t>1.1.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:49:44+00:00</t>
+    <t>2026-10-20T08:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1455,7 +1455,7 @@
     <t>Sted for episoden</t>
   </si>
   <si>
-    <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
+    <t>Organisasjonen episoden fant sted ved. Hvis episoden gjelder hele innleggelsen og ikke gjenspeiler pasientens forflytninger mellom avdelinger, kan organisasjonen for den enkelte administreringen eller rekvireringen angis med administrertVed i Legemiddeladministrering og rekvirertVed i Legemiddelrekvirering.</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
